--- a/public/assets/documents/excel/sample_upload/TrainingSchedule.xlsx
+++ b/public/assets/documents/excel/sample_upload/TrainingSchedule.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deveopers\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xampp\82\htdocs\NeoEHS_Karam\public\assets\documents\excel\sample_upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,29 +13,35 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="1"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>SNo</t>
   </si>
   <si>
+    <t>From Date</t>
+  </si>
+  <si>
+    <t>To Date</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Topic Name</t>
+  </si>
+  <si>
+    <t>Trainer Name</t>
+  </si>
+  <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>From Date</t>
-  </si>
-  <si>
-    <t>To Date</t>
-  </si>
-  <si>
-    <t>Topic Name</t>
-  </si>
-  <si>
-    <t>Trainer Name</t>
   </si>
   <si>
     <t>Department</t>
@@ -51,7 +56,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -71,13 +76,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -94,14 +93,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -110,10 +101,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -359,43 +350,42 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="8.855469" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="17.14063" customWidth="1"/>
+    <col min="6" max="6" width="34.71094" customWidth="1"/>
+    <col min="7" max="7" width="14.85547" customWidth="1"/>
+    <col min="8" max="8" width="21.14063" customWidth="1"/>
+    <col min="9" max="9" width="24.28516" customWidth="1"/>
+    <col min="10" max="10" width="20.71094" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -405,6 +395,12 @@
       </c>
       <c r="I1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
